--- a/artfynd/A 64406-2023 artfynd.xlsx
+++ b/artfynd/A 64406-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118602522</v>
+        <v>118602440</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462743</v>
+        <v>462098</v>
       </c>
       <c r="R2" t="n">
-        <v>6824587</v>
+        <v>6825005</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118602433</v>
+        <v>118602554</v>
       </c>
       <c r="B3" t="n">
-        <v>79102</v>
+        <v>86820</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462661</v>
+        <v>462357</v>
       </c>
       <c r="R3" t="n">
-        <v>6824659</v>
+        <v>6824835</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118602465</v>
+        <v>118602433</v>
       </c>
       <c r="B4" t="n">
-        <v>57306</v>
+        <v>79102</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,42 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Landledaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462477</v>
+        <v>462661</v>
       </c>
       <c r="R4" t="n">
-        <v>6824771</v>
+        <v>6824659</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118602554</v>
+        <v>118602532</v>
       </c>
       <c r="B5" t="n">
-        <v>86820</v>
+        <v>78484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462357</v>
+        <v>462296</v>
       </c>
       <c r="R5" t="n">
-        <v>6824835</v>
+        <v>6824906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118602532</v>
+        <v>118602465</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,34 +1099,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Landledaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462296</v>
+        <v>462477</v>
       </c>
       <c r="R6" t="n">
-        <v>6824906</v>
+        <v>6824771</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118602524</v>
+        <v>118602454</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462359</v>
+        <v>462453</v>
       </c>
       <c r="R7" t="n">
-        <v>6824847</v>
+        <v>6824785</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118602479</v>
+        <v>118602522</v>
       </c>
       <c r="B8" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,21 +1311,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462543</v>
+        <v>462743</v>
       </c>
       <c r="R8" t="n">
-        <v>6824745</v>
+        <v>6824587</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118602440</v>
+        <v>118602524</v>
       </c>
       <c r="B9" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1413,21 +1413,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462098</v>
+        <v>462359</v>
       </c>
       <c r="R9" t="n">
-        <v>6825005</v>
+        <v>6824847</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118602454</v>
+        <v>118602479</v>
       </c>
       <c r="B10" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,21 +1515,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462453</v>
+        <v>462543</v>
       </c>
       <c r="R10" t="n">
-        <v>6824785</v>
+        <v>6824745</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 64406-2023 artfynd.xlsx
+++ b/artfynd/A 64406-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118602440</v>
+        <v>118602433</v>
       </c>
       <c r="B2" t="n">
         <v>79102</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462098</v>
+        <v>462661</v>
       </c>
       <c r="R2" t="n">
-        <v>6825005</v>
+        <v>6824659</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118602554</v>
+        <v>118602465</v>
       </c>
       <c r="B3" t="n">
-        <v>86820</v>
+        <v>57306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Landledaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462357</v>
+        <v>462477</v>
       </c>
       <c r="R3" t="n">
-        <v>6824835</v>
+        <v>6824771</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118602433</v>
+        <v>118602479</v>
       </c>
       <c r="B4" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462661</v>
+        <v>462543</v>
       </c>
       <c r="R4" t="n">
-        <v>6824659</v>
+        <v>6824745</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118602465</v>
+        <v>118602524</v>
       </c>
       <c r="B6" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,42 +1107,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Landledaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462477</v>
+        <v>462359</v>
       </c>
       <c r="R6" t="n">
-        <v>6824771</v>
+        <v>6824847</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118602454</v>
+        <v>118602522</v>
       </c>
       <c r="B7" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462453</v>
+        <v>462743</v>
       </c>
       <c r="R7" t="n">
-        <v>6824785</v>
+        <v>6824587</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118602522</v>
+        <v>118602454</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,21 +1311,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462743</v>
+        <v>462453</v>
       </c>
       <c r="R8" t="n">
-        <v>6824587</v>
+        <v>6824785</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118602524</v>
+        <v>118602440</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1413,21 +1413,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462359</v>
+        <v>462098</v>
       </c>
       <c r="R9" t="n">
-        <v>6824847</v>
+        <v>6825005</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118602479</v>
+        <v>118602554</v>
       </c>
       <c r="B10" t="n">
-        <v>78221</v>
+        <v>86820</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,21 +1515,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462543</v>
+        <v>462357</v>
       </c>
       <c r="R10" t="n">
-        <v>6824745</v>
+        <v>6824835</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 64406-2023 artfynd.xlsx
+++ b/artfynd/A 64406-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118602433</v>
+        <v>118602522</v>
       </c>
       <c r="B2" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462661</v>
+        <v>462743</v>
       </c>
       <c r="R2" t="n">
-        <v>6824659</v>
+        <v>6824587</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118602465</v>
+        <v>118602440</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
+        <v>79109</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Landledaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462477</v>
+        <v>462098</v>
       </c>
       <c r="R3" t="n">
-        <v>6824771</v>
+        <v>6825005</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +882,7 @@
         <v>118602479</v>
       </c>
       <c r="B4" t="n">
-        <v>78221</v>
+        <v>78228</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -992,7 +984,7 @@
         <v>118602532</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1094,7 +1086,7 @@
         <v>118602524</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118602522</v>
+        <v>118602454</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>79080</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462743</v>
+        <v>462453</v>
       </c>
       <c r="R7" t="n">
-        <v>6824587</v>
+        <v>6824785</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118602454</v>
+        <v>118602554</v>
       </c>
       <c r="B8" t="n">
-        <v>79073</v>
+        <v>86827</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462453</v>
+        <v>462357</v>
       </c>
       <c r="R8" t="n">
-        <v>6824785</v>
+        <v>6824835</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118602440</v>
+        <v>118602433</v>
       </c>
       <c r="B9" t="n">
-        <v>79102</v>
+        <v>79109</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462098</v>
+        <v>462661</v>
       </c>
       <c r="R9" t="n">
-        <v>6825005</v>
+        <v>6824659</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118602554</v>
+        <v>118602465</v>
       </c>
       <c r="B10" t="n">
-        <v>86820</v>
+        <v>57306</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,34 +1507,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Landledaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462357</v>
+        <v>462477</v>
       </c>
       <c r="R10" t="n">
-        <v>6824835</v>
+        <v>6824771</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 64406-2023 artfynd.xlsx
+++ b/artfynd/A 64406-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118602522</v>
+        <v>118602433</v>
       </c>
       <c r="B2" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462743</v>
+        <v>462661</v>
       </c>
       <c r="R2" t="n">
-        <v>6824587</v>
+        <v>6824659</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118602440</v>
+        <v>118602454</v>
       </c>
       <c r="B3" t="n">
-        <v>79109</v>
+        <v>79080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462098</v>
+        <v>462453</v>
       </c>
       <c r="R3" t="n">
-        <v>6825005</v>
+        <v>6824785</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118602479</v>
+        <v>118602465</v>
       </c>
       <c r="B4" t="n">
-        <v>78228</v>
+        <v>57306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Landledaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462543</v>
+        <v>462477</v>
       </c>
       <c r="R4" t="n">
-        <v>6824745</v>
+        <v>6824771</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1185,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118602454</v>
+        <v>118602554</v>
       </c>
       <c r="B7" t="n">
-        <v>79080</v>
+        <v>86827</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462453</v>
+        <v>462357</v>
       </c>
       <c r="R7" t="n">
-        <v>6824785</v>
+        <v>6824835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118602554</v>
+        <v>118602522</v>
       </c>
       <c r="B8" t="n">
-        <v>86827</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1311,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462357</v>
+        <v>462743</v>
       </c>
       <c r="R8" t="n">
-        <v>6824835</v>
+        <v>6824587</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1397,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118602433</v>
+        <v>118602440</v>
       </c>
       <c r="B9" t="n">
         <v>79109</v>
@@ -1429,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462661</v>
+        <v>462098</v>
       </c>
       <c r="R9" t="n">
-        <v>6824659</v>
+        <v>6825005</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118602465</v>
+        <v>118602479</v>
       </c>
       <c r="B10" t="n">
-        <v>57306</v>
+        <v>78228</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,42 +1515,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Landledaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462477</v>
+        <v>462543</v>
       </c>
       <c r="R10" t="n">
-        <v>6824771</v>
+        <v>6824745</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
